--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486858_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486858_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.6599</v>
+        <v>8.8757</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9528</v>
+        <v>7.2279</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7071</v>
+        <v>1.6478</v>
       </c>
       <c r="G2" t="n">
         <v>5.5442</v>
@@ -610,13 +610,13 @@
         <v>3.0801</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.147</v>
+        <v>-1.9312</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9068000000000001</v>
+        <v>-0.6317</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.2403</v>
+        <v>-1.2996</v>
       </c>
       <c r="V2" t="n">
         <v>3.2094</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2228</v>
+        <v>2.1603</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2792</v>
+        <v>1.3649</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9436</v>
+        <v>0.7954</v>
       </c>
       <c r="G3" t="n">
         <v>1.6517</v>
@@ -688,13 +688,13 @@
         <v>2.2588</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1255</v>
+        <v>0.063</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1853</v>
+        <v>0.271</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0598</v>
+        <v>-0.208</v>
       </c>
       <c r="V3" t="n">
         <v>0.2402</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7956</v>
+        <v>2.1265</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.106</v>
+        <v>-0.2493</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9016</v>
+        <v>2.3758</v>
       </c>
       <c r="G4" t="n">
         <v>4.5131</v>
@@ -766,13 +766,13 @@
         <v>2.6694</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0399</v>
+        <v>-0.7089</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0272</v>
+        <v>-0.1706</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0126</v>
+        <v>-0.5384</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2402</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7343</v>
+        <v>1.6419</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3521</v>
+        <v>0.4072</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0864</v>
+        <v>1.2346</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7517</v>
@@ -844,13 +844,13 @@
         <v>2.8748</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.1095</v>
+        <v>-1.202</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0462</v>
+        <v>-0.2869</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0633</v>
+        <v>-0.9151</v>
       </c>
       <c r="V5" t="n">
         <v>0.7207</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0703</v>
+        <v>-0.589</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.275</v>
+        <v>-2.934</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2047</v>
+        <v>2.345</v>
       </c>
       <c r="G6" t="n">
         <v>1.4254</v>
@@ -922,13 +922,13 @@
         <v>3.2855</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8285</v>
+        <v>-1.3471</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9804</v>
+        <v>-0.6394</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1519</v>
+        <v>-0.7077</v>
       </c>
       <c r="V6" t="n">
         <v>-1.8993</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. OKEKE</t>
+          <t>J. ZHAO OLMOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1178</v>
+        <v>-1.5385</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0731</v>
+        <v>-5.2956</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0447</v>
+        <v>3.7571</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0066</v>
+        <v>2.6291</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.425</v>
+        <v>-0.2918</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4184</v>
+        <v>2.9208</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0195</v>
+        <v>2.2829</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0195</v>
+        <v>0.4808</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.802</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0261</v>
+        <v>0.3462</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4445</v>
+        <v>-0.7726</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4184</v>
+        <v>1.1188</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.0267</v>
+        <v>-3.4908</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0267</v>
+        <v>-7.187</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.6962</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.604</v>
+        <v>-1.724</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0659</v>
+        <v>-0.3915</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5381</v>
+        <v>-1.3325</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.4805</v>
+        <v>1.0472</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4805</v>
+        <v>1.0472</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1181</v>
+        <v>-1.979</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3548</v>
+        <v>-0.3936</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7633</v>
+        <v>-1.5854</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0658</v>
@@ -1078,13 +1078,13 @@
         <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1058</v>
+        <v>-0.9666</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0541</v>
+        <v>0.0154</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.1598</v>
+        <v>-0.982</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1786</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. KNOWLES</t>
+          <t>I. OKEKE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1596</v>
+        <v>-2.0882</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6445</v>
+        <v>-1.0731</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5151</v>
+        <v>-1.015</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0725</v>
+        <v>-0.0066</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5904</v>
+        <v>-0.425</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6629</v>
+        <v>0.4184</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3637</v>
+        <v>0.0195</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2847</v>
+        <v>0.0195</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0789</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4362</v>
+        <v>-0.0261</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6943</v>
+        <v>-0.4445</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7418</v>
+        <v>0.4184</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6427</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4107</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6029</v>
+        <v>-0.5743</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4416</v>
+        <v>-0.0659</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1613</v>
+        <v>-0.5085</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0472</v>
+        <v>-0.4805</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.3963</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3491</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. ZHAO OLMOS</t>
+          <t>D. KNOWLES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4831</v>
+        <v>-2.4874</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.8845</v>
+        <v>-1.8537</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4014</v>
+        <v>-0.6337</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6291</v>
+        <v>-0.0725</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2918</v>
+        <v>0.5904</v>
       </c>
       <c r="I10" t="n">
-        <v>2.9208</v>
+        <v>-0.6629</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2829</v>
+        <v>1.3637</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4808</v>
+        <v>1.2847</v>
       </c>
       <c r="L10" t="n">
-        <v>1.802</v>
+        <v>0.0789</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3462</v>
+        <v>-1.4362</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7726</v>
+        <v>-0.6943</v>
       </c>
       <c r="O10" t="n">
-        <v>1.1188</v>
+        <v>-0.7418</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.4908</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q10" t="n">
-        <v>-7.187</v>
+        <v>-2.0534</v>
       </c>
       <c r="R10" t="n">
-        <v>3.6962</v>
+        <v>0.4107</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.6686</v>
+        <v>0.2751</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9804</v>
+        <v>0.2324</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.6882</v>
+        <v>0.0427</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0472</v>
+        <v>-1.0472</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-1.3963</v>
       </c>
       <c r="X10" t="n">
-        <v>1.0472</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5.463699999999999</v>
+        <v>6.1223</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.458</v>
+        <v>-2.799300000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>8.921700000000001</v>
+        <v>8.9216</v>
       </c>
       <c r="G11" t="n">
         <v>13.8669</v>
@@ -1312,13 +1312,13 @@
         <v>19.5076</v>
       </c>
       <c r="S11" t="n">
-        <v>-8.774899999999999</v>
+        <v>-8.116</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.3259</v>
+        <v>-1.6672</v>
       </c>
       <c r="U11" t="n">
-        <v>-6.4489</v>
+        <v>-6.4491</v>
       </c>
       <c r="V11" t="n">
         <v>0.3717000000000004</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.6328</v>
+        <v>4.8332</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1821</v>
+        <v>2.3914</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4506</v>
+        <v>2.4419</v>
       </c>
       <c r="G12" t="n">
         <v>1.0885</v>
@@ -1390,13 +1390,13 @@
         <v>2.2588</v>
       </c>
       <c r="S12" t="n">
-        <v>1.265</v>
+        <v>1.4655</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0072</v>
+        <v>1.2164</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2578</v>
+        <v>0.249</v>
       </c>
       <c r="V12" t="n">
         <v>1.0472</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. TOLEDO ZAMORA</t>
+          <t>A. DUVAL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6531</v>
+        <v>2.8776</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2417</v>
+        <v>2.1604</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8948</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.4614</v>
+        <v>0.5607</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.1537</v>
+        <v>-0.5386</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.3077</v>
+        <v>1.0993</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.947</v>
+        <v>1.9594</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6837</v>
+        <v>1.2103</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2633</v>
+        <v>0.7491</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5144</v>
+        <v>-1.3987</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.47</v>
+        <v>-1.7489</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0445</v>
+        <v>0.3502</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>1.4374</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2588</v>
+        <v>-0.2053</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2588</v>
+        <v>1.6427</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7798</v>
+        <v>0.399</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7853</v>
+        <v>0.0347</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9944</v>
+        <v>0.3643</v>
       </c>
       <c r="V13" t="n">
-        <v>2.3347</v>
+        <v>0.4805</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1786</v>
+        <v>0.3716</v>
       </c>
       <c r="X13" t="n">
-        <v>1.1561</v>
+        <v>0.1088</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. DUVAL</t>
+          <t>C. TOLEDO ZAMORA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1829</v>
+        <v>1.1572</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2189</v>
+        <v>-1.6016</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.036</v>
+        <v>2.7588</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5607</v>
+        <v>-3.4614</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5386</v>
+        <v>-2.1537</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0993</v>
+        <v>-1.3077</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9594</v>
+        <v>-1.947</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2103</v>
+        <v>-0.6837</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7491</v>
+        <v>-1.2633</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3987</v>
+        <v>-1.5144</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.7489</v>
+        <v>-1.47</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3502</v>
+        <v>-0.0445</v>
       </c>
       <c r="P14" t="n">
-        <v>1.4374</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2053</v>
+        <v>-2.2588</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6427</v>
+        <v>2.2588</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2956</v>
+        <v>2.2839</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9068000000000001</v>
+        <v>1.4255</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3889</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4805</v>
+        <v>2.3347</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3716</v>
+        <v>1.1786</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1088</v>
+        <v>1.1561</v>
       </c>
     </row>
     <row r="15">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1021</v>
+        <v>-0.0392</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0807</v>
+        <v>-0.9761</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1828</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>-0.1602</v>
@@ -1702,13 +1702,13 @@
         <v>1.2321</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0837</v>
+        <v>0.9424</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3757</v>
+        <v>0.4803</v>
       </c>
       <c r="U16" t="n">
-        <v>0.708</v>
+        <v>0.4621</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. MILADINOVIC</t>
+          <t>M. MUKENDI MUKENDI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2011</v>
+        <v>-0.324</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8859</v>
+        <v>0.4563</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6848</v>
+        <v>-0.7803</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4568</v>
+        <v>-0.3016</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1752</v>
+        <v>-0.1491</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2816</v>
+        <v>-0.1525</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9588</v>
+        <v>1.4289</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8404</v>
+        <v>1.35</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1184</v>
+        <v>0.0789</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.502</v>
+        <v>-1.7305</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6653</v>
+        <v>-1.4991</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1632</v>
+        <v>-0.2314</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.6694</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.0801</v>
+        <v>-1.2321</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="S17" t="n">
-        <v>2.1204</v>
+        <v>0.2178</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3443</v>
+        <v>0.0192</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7761</v>
+        <v>0.1986</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1088</v>
+        <v>-0.2402</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.1088</v>
+        <v>0.2402</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. MUKENDI MUKENDI</t>
+          <t>G. MILADINOVIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.657</v>
+        <v>-1.0362</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3517</v>
+        <v>-1.5135</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0087</v>
+        <v>0.4773</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3016</v>
+        <v>0.4568</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1491</v>
+        <v>0.1752</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1525</v>
+        <v>0.2816</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4289</v>
+        <v>0.9588</v>
       </c>
       <c r="K18" t="n">
-        <v>1.35</v>
+        <v>0.8404</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0789</v>
+        <v>0.1184</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7305</v>
+        <v>-0.502</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4991</v>
+        <v>-0.6653</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2314</v>
+        <v>0.1632</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-2.6694</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.2321</v>
+        <v>-3.0801</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2321</v>
+        <v>0.4107</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1152</v>
+        <v>1.2853</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0854</v>
+        <v>0.7167</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0298</v>
+        <v>0.5687</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2402</v>
+        <v>-0.1088</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2402</v>
+        <v>-0.1088</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8592</v>
+        <v>-1.5227</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.0799</v>
+        <v>-3.2891</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2206</v>
+        <v>1.7664</v>
       </c>
       <c r="G19" t="n">
         <v>-1.381</v>
@@ -1936,13 +1936,13 @@
         <v>2.4641</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3904</v>
+        <v>1.7269</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2589</v>
+        <v>1.0497</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1315</v>
+        <v>0.6772</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0472</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4993</v>
+        <v>-2.1123</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1776</v>
+        <v>-0.9684</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3217</v>
+        <v>-1.1439</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1141</v>
@@ -2014,13 +2014,13 @@
         <v>1.4374</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2308</v>
+        <v>0.6179</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3912</v>
+        <v>0.6004</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1604</v>
+        <v>0.0175</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. TAVELLI</t>
+          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6138</v>
+        <v>-2.2066</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5682</v>
+        <v>-2.2026</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.182</v>
+        <v>-0.004</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.272</v>
+        <v>-2.8971</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2272</v>
+        <v>-1.9626</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0448</v>
+        <v>-0.9345</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9588</v>
+        <v>-1.0479</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0512</v>
+        <v>-0.6</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.4479</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2308</v>
+        <v>-1.8492</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2783</v>
+        <v>-1.3626</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0475</v>
+        <v>-0.4866</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2053</v>
+        <v>1.4374</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8481</v>
+        <v>2.4641</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2208</v>
+        <v>-0.2664</v>
       </c>
       <c r="T21" t="n">
-        <v>0.244</v>
+        <v>-0.128</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0232</v>
+        <v>-0.1385</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.3573</v>
+        <v>-0.4805</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.7761</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
+          <t>J. TAVELLI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7</v>
+        <v>-2.3</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7256</v>
+        <v>0.882</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0256</v>
+        <v>-3.182</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.8971</v>
+        <v>-0.272</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.9626</v>
+        <v>-0.2272</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9345</v>
+        <v>-0.0448</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0479</v>
+        <v>0.9588</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6</v>
+        <v>1.0512</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4479</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8492</v>
+        <v>-1.2308</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3626</v>
+        <v>-1.2783</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4866</v>
+        <v>0.0475</v>
       </c>
       <c r="P22" t="n">
-        <v>1.4374</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4641</v>
+        <v>1.8481</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7598</v>
+        <v>0.5346</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.651</v>
+        <v>0.5578</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1088</v>
+        <v>-0.0232</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.4805</v>
+        <v>-2.3573</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.4805</v>
+        <v>-3.7761</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7791</v>
+        <v>-3.671</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8699</v>
+        <v>-4.0791</v>
       </c>
       <c r="F23" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.4082</v>
       </c>
       <c r="G23" t="n">
         <v>-5.2497</v>
@@ -2248,13 +2248,13 @@
         <v>1.8481</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8546</v>
+        <v>0.9627</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6856</v>
+        <v>0.4764</v>
       </c>
       <c r="U23" t="n">
-        <v>0.169</v>
+        <v>0.4863</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.4636</v>
+        <v>-4.068999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.6815</v>
+        <v>-8.6814</v>
       </c>
       <c r="F24" t="n">
-        <v>3.217599999999999</v>
+        <v>4.612600000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-13.8668</v>
@@ -2317,7 +2317,7 @@
         <v>-1.3795</v>
       </c>
       <c r="P24" t="n">
-        <v>0.0001000000000003221</v>
+        <v>0.0001000000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>-19.5075</v>
@@ -2326,16 +2326,16 @@
         <v>19.5077</v>
       </c>
       <c r="S24" t="n">
-        <v>8.774900000000001</v>
+        <v>10.1696</v>
       </c>
       <c r="T24" t="n">
-        <v>6.448999999999999</v>
+        <v>6.4491</v>
       </c>
       <c r="U24" t="n">
-        <v>2.325699999999999</v>
+        <v>3.7204</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3715999999999998</v>
+        <v>-0.3715999999999997</v>
       </c>
       <c r="W24" t="n">
         <v>3.123000000000001</v>
